--- a/Projects/CoolingTestBench/documents/RADIATOR TEST BENCH.xlsx
+++ b/Projects/CoolingTestBench/documents/RADIATOR TEST BENCH.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ccmee\ccmeelboom\Projects\CoolingTestBench\documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ccmee\AER27\Powertrain\Cooling System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CBE3FCC-B627-4D0C-B476-9AE423AD555E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3747492-C9F1-4A57-8582-68543B7A8BE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{51EC7F9C-3E44-4016-9480-00656B64CE9B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="3" xr2:uid="{51EC7F9C-3E44-4016-9480-00656B64CE9B}"/>
   </bookViews>
   <sheets>
     <sheet name="MATERIALS &amp; BUDGET DRAFT" sheetId="1" r:id="rId1"/>
     <sheet name="REASONING" sheetId="2" r:id="rId2"/>
-    <sheet name="BILL OF MATERIALS " sheetId="4" r:id="rId3"/>
-    <sheet name="BLOCK DIAGRAM" sheetId="3" r:id="rId4"/>
+    <sheet name="BLOCK DIAGRAM" sheetId="3" r:id="rId3"/>
+    <sheet name="BILL OF MATERIALS " sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="128">
   <si>
     <t>WATER TANKS</t>
   </si>
@@ -159,9 +159,39 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">Water Tank </t>
+  </si>
+  <si>
+    <t>Needed to hold water for cooling system</t>
+  </si>
+  <si>
     <t>Barbed Hose Fitting</t>
   </si>
   <si>
+    <t>Needed to transition garden hose thread to hose barb for cooling tubes</t>
+  </si>
+  <si>
+    <t>Braid Reenforced PVC Tubing</t>
+  </si>
+  <si>
+    <t>Extra tubing with heat resistance in in case what we have is either not enough or does not work well with test system</t>
+  </si>
+  <si>
+    <t>Reads voltage within system and delivers value to arduino for computer data storage, this is then converted to pressure</t>
+  </si>
+  <si>
+    <t>Needed to conect pressure transducer to test system</t>
+  </si>
+  <si>
+    <t>10AN Female to Hose Barb</t>
+  </si>
+  <si>
+    <t>Needed to implement radiator into testing system</t>
+  </si>
+  <si>
+    <t>* WILL BE ELABORATED ON IN A DOCUMENT</t>
+  </si>
+  <si>
     <t>REV 0</t>
   </si>
   <si>
@@ -408,49 +438,52 @@
     <t>Allow wood plank to be foldable for good storage</t>
   </si>
   <si>
-    <t>5 Gallon Bucket</t>
-  </si>
-  <si>
-    <t>This section cover the reasoning behind each of the selected parts for the test bench, the goal is to put reasoning, assembly, and results in a paper by the end of the year.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The easiest, cheapest and most practical way of making a resivoir is attaching a bulkhead to the bottom of the bucket. Bulkheads connect directly to an NPT male fitting making the consequent barb adapter easy to find. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">The barbed fitting is a fitting we have always used and is easy and cheap to implement. </t>
-  </si>
-  <si>
-    <t>Clear Vinyl Tubing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This is the same type of tubing used in previous years. The tubing is resistnet to up to 170 degrees farenheit and 55 psi which is far more than the 13 psi maximum we expect to test at. </t>
-  </si>
-  <si>
-    <t>There are four pressure sensors found on the test bench. The first two come before and after the pump. One item that is not provided in the Bosch pump documentation is efficiney, these pressure sensors will allow us to find actual pressure values; comparing them to the input power, efficiency can be derived.The second two pressure transducers are placed before and after the radiator, these sendors will output input and output pressures, testing at different flow rates, we can find a minor loss coefficient for the radiator that is attached to the test bench.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The splicer is necessary to mount the pressure sensors. </t>
-  </si>
-  <si>
-    <t>Pressure Sensors</t>
-  </si>
-  <si>
-    <t>Flow Meter</t>
-  </si>
-  <si>
-    <t>The flowmeter is crucial to determining the flow rate at a specific pump PWM input. Plotting flow versus the pressure loss of the radiator will give a line from which the minor loss coefficient can be found.</t>
-  </si>
-  <si>
-    <t>Tube Sizing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tube sizing was kept constant at 3/4" throughout the whole test bench in order to reduce losses from decreasers and increasers. </t>
-  </si>
-  <si>
-    <t>Connections</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The pump requires a 12V connection and the pressure sensors and flowmeter each require 5V. Four pressure sensors and one flowmeter require a significant amount of current which an Arduino UNO alone cannot supply, to mitigate this, these sensors will be powered on a breadboard where the power is supplied by a 5V DC power adapter connected to a jack barrel on the breadboard. The pump will be connected directly  to an external 12V battey. The PWM and feedback wires for the pump and sensors will be connected to an Arduino UNO where PWM values will be inputted and feedback will be read and saved through the serial monitor. </t>
+    <t>DONE</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>POTENTIAL RADIATORS TO TEST</t>
+  </si>
+  <si>
+    <t>https://www.alibaba.com/product-detail/120mm-High-Performance-Aluminum-Radiator-Industrial_1601803359808.html?spm=a2700.prosearch.normal_offer.d_title.67b767afAoQhml&amp;priceId=e4e708cba3ee4debac8f3828d969daea</t>
+  </si>
+  <si>
+    <t>https://www.alibaba.com/product-detail/Computer-Water-Cooling-mini-Heat-Sink_1601715007377.html?spm=a2700.prosearch.normal_offer.d_image.67b767afAoQhml&amp;priceId=7ec269ca32ff42029f46a576ca7cc97b</t>
+  </si>
+  <si>
+    <t>https://www.alibaba.com/product-detail/GX9225-DC-24v-Fan-0-52A_1600764754053.html?spm=a2700.prosearch.normal_offer.d_image.67b767afAoQhml&amp;priceId=ea54a127782d4b2ba0c15037a7d02148</t>
+  </si>
+  <si>
+    <t>https://www.alibaba.com/product-detail/6-Small-sized-Cooling-Radiators-Are_1601560620241.html?spm=a2700.prosearch.normal_offer.d_image.67b767afAoQhml&amp;priceId=c85c0b1d8d9c4d0692be27caa8d1f029</t>
+  </si>
+  <si>
+    <t>https://www.alibaba.com/product-detail/80mm-Aluminum-Radiator-With-OD9-5mm_60692622546.html?spm=a2700.prosearch.normal_offer.d_image.67b767afAoQhml&amp;priceId=c85c0b1d8d9c4d0692be27caa8d1f029</t>
+  </si>
+  <si>
+    <t>https://www.alibaba.com/product-detail/Small-Water-Cooling-Radiator-Aluminum-Medical_1600845196049.html?spm=a2700.prosearch.normal_offer.d_image.67b767afAoQhml&amp;priceId=98085792f01c48269821f98346552af1</t>
+  </si>
+  <si>
+    <t>https://www.alibaba.com/product-detail/High-Performance-Custom-Aluminum-Radiator-Cooling_1601283659123.html?spm=a2700.prosearch.normal_offer.d_image.67b767afAoQhml&amp;priceId=b9cb5c253f2c42b6b78e23a3dc96f07c</t>
+  </si>
+  <si>
+    <t>FAN</t>
+  </si>
+  <si>
+    <t>https://www.homedepot.com/p/POWERTEC-36-in-Universal-T-Track-for-Woodworking-2-Pack-71119/308181854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T Track to mount fitting clamps </t>
+  </si>
+  <si>
+    <t>Home Depot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extruded aluminum t track </t>
+  </si>
+  <si>
+    <t>36 in. Universal T-Track for Woodworking (2-Pack)</t>
   </si>
 </sst>
 </file>
@@ -461,7 +494,7 @@
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -525,8 +558,17 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -578,6 +620,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -751,7 +799,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -810,9 +858,10 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1178,16 +1227,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>60324</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>327024</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>85726</xdr:rowOff>
+      <xdr:rowOff>47626</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
-      <xdr:colOff>394757</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>2118</xdr:rowOff>
+      <xdr:colOff>51857</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>141818</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1219,8 +1268,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="669924" y="8340726"/>
-          <a:ext cx="15523633" cy="7739592"/>
+          <a:off x="327024" y="8429626"/>
+          <a:ext cx="15479183" cy="7876117"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1686,7 +1735,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2224ABA-CDDB-4312-A3E2-276D4D990AF4}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.44140625" bestFit="1" customWidth="1"/>
@@ -1694,72 +1743,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B3" s="44" t="s">
-        <v>104</v>
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="44" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B5" s="44" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B6" s="44" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="44" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B8" s="44" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B9" s="44" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B10" s="44" t="s">
-        <v>116</v>
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1768,8 +1801,32 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81F98FA3-8C1F-45C1-AEE6-349020083CF7}">
+  <dimension ref="B7:B44"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="26" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="7" spans="2:2" ht="31.2" x14ac:dyDescent="0.6">
+      <c r="B7" s="43" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2" ht="31.2" x14ac:dyDescent="0.6">
+      <c r="B44" s="43" t="s">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D9CAD89-431F-4B3C-B414-334AA52899F3}">
-  <dimension ref="B1:K27"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="77.109375" customWidth="1"/>
@@ -1783,57 +1840,61 @@
     <col min="10" max="10" width="50.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>112</v>
+      </c>
       <c r="B5" s="15" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="I5" s="19" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="44"/>
       <c r="B6" s="22" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G6" s="26">
         <v>1</v>
@@ -1842,28 +1903,29 @@
         <v>7.48</v>
       </c>
       <c r="I6" s="27">
-        <f t="shared" ref="I6:I20" si="0">H6*G6</f>
+        <f t="shared" ref="I6:I21" si="0">H6*G6</f>
         <v>7.48</v>
       </c>
       <c r="J6" s="28" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="44"/>
       <c r="B7" s="29" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G7" s="20">
         <v>1</v>
@@ -1876,24 +1938,25 @@
         <v>12.99</v>
       </c>
       <c r="J7" s="30" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="44"/>
       <c r="B8" s="29" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G8" s="13">
         <v>1</v>
@@ -1906,24 +1969,25 @@
         <v>4.28</v>
       </c>
       <c r="J8" s="30" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="44"/>
       <c r="B9" s="29" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G9" s="13">
         <v>1</v>
@@ -1936,24 +2000,27 @@
         <v>23.66</v>
       </c>
       <c r="J9" s="30" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>113</v>
+      </c>
       <c r="B10" s="31" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="G10" s="13">
         <v>4</v>
@@ -1966,24 +2033,25 @@
         <v>272</v>
       </c>
       <c r="J10" s="30" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="K10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="44"/>
       <c r="B11" s="32" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>14</v>
@@ -1999,24 +2067,25 @@
         <v>91.96</v>
       </c>
       <c r="J11" s="30" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="44"/>
       <c r="B12" s="33" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="G12" s="13">
         <v>1</v>
@@ -2029,24 +2098,27 @@
         <v>26.99</v>
       </c>
       <c r="J12" s="30" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>113</v>
+      </c>
       <c r="B13" s="33" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="G13" s="13">
         <v>2</v>
@@ -2059,24 +2131,25 @@
         <v>19.899999999999999</v>
       </c>
       <c r="J13" s="30" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="44"/>
       <c r="B14" s="33" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G14" s="13">
         <v>2</v>
@@ -2089,24 +2162,27 @@
         <v>12.88</v>
       </c>
       <c r="J14" s="30" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>113</v>
+      </c>
       <c r="B15" s="40" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G15" s="13">
         <v>1</v>
@@ -2119,24 +2195,27 @@
         <v>4.25</v>
       </c>
       <c r="J15" s="30" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>113</v>
+      </c>
       <c r="B16" s="33" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="G16" s="13">
         <v>1</v>
@@ -2149,24 +2228,27 @@
         <v>6.99</v>
       </c>
       <c r="J16" s="30" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="17" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>113</v>
+      </c>
       <c r="B17" s="40" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C17" s="39" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="G17" s="13">
         <v>1</v>
@@ -2179,24 +2261,27 @@
         <v>6.99</v>
       </c>
       <c r="J17" s="30" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="18" spans="2:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>113</v>
+      </c>
       <c r="B18" s="40" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C18" s="41" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="G18" s="13">
         <v>1</v>
@@ -2209,24 +2294,25 @@
         <v>25.99</v>
       </c>
       <c r="J18" s="30" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" s="44"/>
       <c r="B19" s="29" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="C19" s="41" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="G19" s="13">
         <v>1</v>
@@ -2239,61 +2325,126 @@
         <v>11.88</v>
       </c>
       <c r="J19" s="30" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="20" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="34" t="s">
-        <v>98</v>
-      </c>
-      <c r="C20" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="D20" s="35" t="s">
-        <v>99</v>
-      </c>
-      <c r="E20" s="35" t="s">
-        <v>35</v>
-      </c>
-      <c r="F20" s="36" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="44"/>
+      <c r="B20" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="C20" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="G20" s="35">
+      <c r="D20" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="G20" s="13">
+        <v>3</v>
+      </c>
+      <c r="H20" s="9">
+        <v>25.21</v>
+      </c>
+      <c r="I20" s="9">
+        <f t="shared" si="0"/>
+        <v>75.63</v>
+      </c>
+      <c r="J20" s="30" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>113</v>
+      </c>
+      <c r="B21" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" s="42" t="s">
+        <v>100</v>
+      </c>
+      <c r="D21" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="E21" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="G21" s="35">
         <v>2</v>
       </c>
-      <c r="H20" s="37">
+      <c r="H21" s="37">
         <v>3.98</v>
       </c>
-      <c r="I20" s="37">
+      <c r="I21" s="37">
         <f t="shared" si="0"/>
         <v>7.96</v>
       </c>
-      <c r="J20" s="38" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="I21" s="11">
-        <f>SUM(I6:I20)</f>
-        <v>536.19999999999993</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B24" s="1"/>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B25" s="1"/>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B26" s="1"/>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B27" s="1"/>
+      <c r="J21" s="38" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I22" s="11">
+        <f>SUM(I6:I21)</f>
+        <v>611.82999999999993</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C23" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="D23" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="46" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B25" s="45" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B26" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B27" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B28" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
+        <v>121</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F11" r:id="rId1" display="https://www.ictbillet.com/products/3-4-hose-barb-750-inch-w-1-8-npt-steam-port-splice-coupler-fitting-adapter?variant=46047867371750&amp;country=US&amp;currency=USD&amp;utm_medium=product_sync&amp;utm_source=google&amp;utm_content=sag_organic&amp;utm_campaign=sag_organic&amp;gad_source=1&amp;gad_campaignid=22606207890&amp;gbraid=0AAAAADn6FEDFVoGAViEuxjchYHteARt-K&amp;gclid=CjwKCAjw2rrQBhBuEiwAarLWHYcdwUHAuR6BgQA7YP0i-q8P2pOOhNP7bPwVl7RVYkn0BT7c1FxyzBoCtk4QAvD_BwE" xr:uid="{396688F0-E230-4530-AA5D-9B0B64432C6D}"/>
-    <hyperlink ref="F20" r:id="rId2" xr:uid="{3FEC9494-43F8-4F2F-89E9-213A31EFECF3}"/>
+    <hyperlink ref="F21" r:id="rId2" xr:uid="{3FEC9494-43F8-4F2F-89E9-213A31EFECF3}"/>
     <hyperlink ref="F19" r:id="rId3" xr:uid="{94B5338F-C35A-4CB1-B812-B18160231072}"/>
     <hyperlink ref="F6" r:id="rId4" xr:uid="{6D9A9467-09DA-4EE6-9106-047BC9193811}"/>
     <hyperlink ref="F7" r:id="rId5" xr:uid="{EEC72439-A52E-4051-8496-FDE4F6CCA273}"/>
@@ -2308,38 +2459,32 @@
     <hyperlink ref="F15" r:id="rId14" display="https://www.amazon.com/Inches-Plumbers-Plumbing-Plumber-Sealing/dp/B091913Z7F/ref=sr_1_3?crid=2RMBBOZ4T6IAV&amp;dib=eyJ2IjoiMSJ9.zXjmjreMCAXZ1xIvG_NIMr_DDDgJiHz1KgTCFs4hj7m8xFG-7fINMYrftBTpPyzxJnSWqNTqrAdNn3RhD3A-wVc5mSehDmkW7p09qvjP7j83HKBRkCQOPkg5OdEQBLAljnEAJyTwmlDdgrF44hBrhbINYkqG0kzTvn9lsTyg4VEPU5tJsjp5T8CGRN26m0oJ3K2ZuZB-o8uqe_wM9bL9jIhrekd0J6a-vVuv9VHW5Cs.uVo6kq5P0LMUpBkKAwjFtfrQ_3nRjxuuegxea4UFOTI&amp;dib_tag=se&amp;keywords=PTFE%2Bthread%2Bseal%2Btape&amp;qid=1779556467&amp;sprefix=asa%2Bfilament%2Caps%2C504&amp;sr=8-3&amp;th=1" xr:uid="{B2C5F6D5-4068-444D-9A7C-D06025AF8E43}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId15"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81F98FA3-8C1F-45C1-AEE6-349020083CF7}">
-  <dimension ref="B7:B44"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="26" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="7" spans="2:2" ht="31.2" x14ac:dyDescent="0.6">
-      <c r="B7" s="43" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="44" spans="2:2" ht="31.2" x14ac:dyDescent="0.6">
-      <c r="B44" s="43" t="s">
-        <v>21</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId15"/>
+  <legacyDrawing r:id="rId16"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100069695D3ACD1134F8D9391614540A2BA" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b2dfc92d52a264ca243413bbdea46b74">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="395d1afe-007a-463d-aa2a-4b4d0d1cace1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dcb7b6c00cd08d160ef6e3c436a0d0d2" ns3:_="">
-    <xsd:import namespace="395d1afe-007a-463d-aa2a-4b4d0d1cace1"/>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="a4c85d7d-04f6-4035-96cb-72842cea6da2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010095070BBE30B57C4EBBAE68589E48C0DE" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bce00f80ac8a8abfc520c9f6cafdf124">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="a4c85d7d-04f6-4035-96cb-72842cea6da2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bba453fc26ba9080ee5bf3d31df7d668" ns3:_="">
+    <xsd:import namespace="a4c85d7d-04f6-4035-96cb-72842cea6da2"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -2350,6 +2495,11 @@
                 <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
                 <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSystemTags" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaLengthInSeconds" minOccurs="0"/>
                 <xsd:element ref="ns3:_activity" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
@@ -2358,7 +2508,7 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="395d1afe-007a-463d-aa2a-4b4d0d1cace1" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="a4c85d7d-04f6-4035-96cb-72842cea6da2" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="MediaServiceDateTaken" ma:index="8" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
@@ -2381,7 +2531,32 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_activity" ma:index="12" nillable="true" ma:displayName="_activity" ma:hidden="true" ma:internalName="_activity">
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="12" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSystemTags" ma:index="13" nillable="true" ma:displayName="MediaServiceSystemTags" ma:hidden="true" ma:internalName="MediaServiceSystemTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="_activity" ma:index="17" nillable="true" ma:displayName="_activity" ma:hidden="true" ma:internalName="_activity">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
@@ -2486,31 +2661,38 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="395d1afe-007a-463d-aa2a-4b4d0d1cace1" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29CEF7C8-30BC-4199-8500-6EE0594C28D3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="a4c85d7d-04f6-4035-96cb-72842cea6da2"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A4FF51F-A26B-4653-AE1B-C98C2711B705}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18422628-6DED-455A-BD1C-6367B375C618}">
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1AD7823-B0B1-4158-B8B9-B5B559E3DB7D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="395d1afe-007a-463d-aa2a-4b4d0d1cace1"/>
+    <ds:schemaRef ds:uri="a4c85d7d-04f6-4035-96cb-72842cea6da2"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
@@ -2519,22 +2701,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29CEF7C8-30BC-4199-8500-6EE0594C28D3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="395d1afe-007a-463d-aa2a-4b4d0d1cace1"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A4FF51F-A26B-4653-AE1B-C98C2711B705}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>